--- a/RaidenDemo/文档/配置表/ConfigValueResource.xlsx
+++ b/RaidenDemo/文档/配置表/ConfigValueResource.xlsx
@@ -26,8 +26,39 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>项目规范</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>常量配置 ID 号段：
+1～999：示例与测试数据
+1000～1999：通用战斗规则
+2000～2999：玩家飞机
+3000～3999：敌机与编队
+4000～4999：掉落物与补给道具
+5000～5999：战斗表现参数
+6000～6999：对象池与性能参数
+7000～7999：资源与表现引用
+ID 只表示业务归属，不编码数据类型；细分业务按百位段划分并预留扩展空间。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="145">
   <si>
     <t>##var</t>
   </si>
@@ -315,6 +346,153 @@
   </si>
   <si>
     <t>对象池_升级道具预热数量</t>
+  </si>
+  <si>
+    <t>着火点_小型火焰特效id列表</t>
+  </si>
+  <si>
+    <t>13101,13102,13103</t>
+  </si>
+  <si>
+    <t>着火点_中型火焰特效id列表</t>
+  </si>
+  <si>
+    <t>13201,13202,13203,13204</t>
+  </si>
+  <si>
+    <t>着火点_大型火焰特效id列表</t>
+  </si>
+  <si>
+    <t>13301,13302,13303</t>
+  </si>
+  <si>
+    <t>着火点_烟雾粒子_小</t>
+  </si>
+  <si>
+    <t>13401</t>
+  </si>
+  <si>
+    <t>着火点_烟雾粒子_中</t>
+  </si>
+  <si>
+    <t>13421</t>
+  </si>
+  <si>
+    <t>着火点_烟雾粒子_大</t>
+  </si>
+  <si>
+    <t>13441</t>
+  </si>
+  <si>
+    <t>着火点的烟雾粒子的生成时间间隔（毫秒）</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>近期伤害统计时长（毫秒）</t>
+  </si>
+  <si>
+    <t>爆炸解体伤害比例阈值（万分比）</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>飞机坠机显示比例下限值</t>
+  </si>
+  <si>
+    <t>飞机下坠速度</t>
+  </si>
+  <si>
+    <t>飞机下坠时角速度范围</t>
+  </si>
+  <si>
+    <t>15,30</t>
+  </si>
+  <si>
+    <t>飞机爆炸间隔时间（毫秒）</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>飞机最后爆炸间隔时间（毫秒）</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>中型_坠地爆炸特效id</t>
+  </si>
+  <si>
+    <t>5101,5102,5103,5104,5105,5106,5107</t>
+  </si>
+  <si>
+    <t>大型_坠地爆炸特效id</t>
+  </si>
+  <si>
+    <t>5201,5202</t>
+  </si>
+  <si>
+    <t>巨型_坠地爆炸特效id</t>
+  </si>
+  <si>
+    <t>5301,5302</t>
+  </si>
+  <si>
+    <t>中型_坠地烟尘特效id</t>
+  </si>
+  <si>
+    <t>大型_坠地烟尘特效id</t>
+  </si>
+  <si>
+    <t>13521,13522,13523</t>
+  </si>
+  <si>
+    <t>巨型_坠地烟尘特效id</t>
+  </si>
+  <si>
+    <t>13541,13542,13543,13544</t>
+  </si>
+  <si>
+    <t>中型_撞击坑散图资源名列表</t>
+  </si>
+  <si>
+    <t>hitHole/small_1</t>
+  </si>
+  <si>
+    <t>大型_撞击坑散图资源名列表</t>
+  </si>
+  <si>
+    <t>hitHole/middle_1</t>
+  </si>
+  <si>
+    <t>巨型_撞击坑散图资源名列表</t>
+  </si>
+  <si>
+    <t>hitHole/big_1</t>
+  </si>
+  <si>
+    <t>小型爆炸特效id列表</t>
+  </si>
+  <si>
+    <t>5001,5002,5003</t>
+  </si>
+  <si>
+    <t>中型爆炸特效id列表</t>
+  </si>
+  <si>
+    <t>大型爆炸特效id列表</t>
+  </si>
+  <si>
+    <t>巨型爆炸特效id列表</t>
+  </si>
+  <si>
+    <t>下坠冒烟特效id列表</t>
+  </si>
+  <si>
+    <t>13560,13561</t>
   </si>
 </sst>
 </file>
@@ -327,7 +505,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,20 +514,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
       <color theme="8" tint="0.6"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="8" tint="0.6"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -361,7 +533,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -509,8 +681,18 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -531,6 +713,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -716,7 +904,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -736,6 +924,21 @@
       </top>
       <bottom style="thin">
         <color theme="0" tint="-0.25"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -838,7 +1041,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -857,137 +1060,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1003,29 +1207,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -1075,6 +1282,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -1094,21 +1302,21 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.4"/>
+          <bgColor theme="9" tint="0.6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.4"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFB48BD9"/>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1126,30 +1334,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>项目规范</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>常量配置 ID 号段：
-1～999：示例与测试数据
-1000～1999：通用战斗规则
-2000～2999：玩家飞机
-3000～3999：敌机与编队
-4000～4999：掉落物与补给道具
-5000～5999：战斗表现参数
-6000～6999：对象池与性能参数
-7000～7999：资源与表现引用
-ID 只表示业务归属，不编码数据类型；细分业务按百位段划分并预留扩展空间。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1410,15 +1594,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" outlineLevelCol="5"/>
+  <dimension ref="A1:F75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="8.375" style="2" customWidth="1"/>
     <col min="3" max="3" width="41.375" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="21.125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="63.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="68.25" style="4" customWidth="1"/>
     <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -2270,24 +2454,1022 @@
         <v>55</v>
       </c>
     </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="9"/>
+      <c r="B48" s="10">
+        <v>7001</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="9"/>
+      <c r="B49" s="10">
+        <v>7002</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="9"/>
+      <c r="B50" s="10">
+        <v>7003</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="9"/>
+      <c r="B51" s="10">
+        <v>7004</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="9"/>
+      <c r="B52" s="10">
+        <v>7005</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="9"/>
+      <c r="B53" s="10">
+        <v>7006</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="9"/>
+      <c r="B54" s="10">
+        <v>7007</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="9"/>
+      <c r="B55" s="10">
+        <v>7010</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="9"/>
+      <c r="B56" s="10">
+        <v>7011</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="9"/>
+      <c r="B57" s="10">
+        <v>7012</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="9"/>
+      <c r="B58" s="10">
+        <v>7013</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="9"/>
+      <c r="B59" s="10">
+        <v>7014</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="9"/>
+      <c r="B60" s="10">
+        <v>7015</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="9"/>
+      <c r="B61" s="10">
+        <v>7016</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="9"/>
+      <c r="B62" s="10">
+        <v>7021</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="9"/>
+      <c r="B63" s="10">
+        <v>7022</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="9"/>
+      <c r="B64" s="10">
+        <v>7023</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="9"/>
+      <c r="B65" s="10">
+        <v>7025</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="12">
+        <v>13501</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="9"/>
+      <c r="B66" s="10">
+        <v>7026</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="9"/>
+      <c r="B67" s="10">
+        <v>7027</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="9"/>
+      <c r="B68" s="10">
+        <v>7031</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="9"/>
+      <c r="B69" s="10">
+        <v>7032</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="9"/>
+      <c r="B70" s="10">
+        <v>7033</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="9"/>
+      <c r="B71" s="10">
+        <v>7041</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="9"/>
+      <c r="B72" s="10">
+        <v>7042</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="9"/>
+      <c r="B73" s="10">
+        <v>7043</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="9"/>
+      <c r="B74" s="10">
+        <v>7044</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="9"/>
+      <c r="B75" s="10">
+        <v>7061</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D4:D1048576">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="D48">
+    <cfRule type="cellIs" dxfId="0" priority="186" operator="equal">
       <formula>"列表"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="172" operator="equal">
       <formula>"Map"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E$1:E$1048576">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+  <conditionalFormatting sqref="E48">
+    <cfRule type="cellIs" dxfId="2" priority="228" operator="equal">
       <formula>"整数"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="214" operator="equal">
       <formula>"浮点数"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="200" operator="equal">
       <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51">
+    <cfRule type="cellIs" dxfId="0" priority="148" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="147" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E51">
+    <cfRule type="cellIs" dxfId="2" priority="146" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="145" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="144" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D52">
+    <cfRule type="cellIs" dxfId="0" priority="143" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="142" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E52">
+    <cfRule type="cellIs" dxfId="2" priority="141" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="140" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="139" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D53">
+    <cfRule type="cellIs" dxfId="0" priority="138" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="137" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E53">
+    <cfRule type="cellIs" dxfId="2" priority="136" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="135" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="134" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D54">
+    <cfRule type="cellIs" dxfId="0" priority="180" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="166" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E54">
+    <cfRule type="cellIs" dxfId="2" priority="133" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="132" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="131" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D55">
+    <cfRule type="cellIs" dxfId="0" priority="130" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="129" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E55">
+    <cfRule type="cellIs" dxfId="2" priority="128" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="127" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="126" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D58">
+    <cfRule type="cellIs" dxfId="1" priority="74" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="75" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E58">
+    <cfRule type="cellIs" dxfId="4" priority="71" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="72" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="73" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D59">
+    <cfRule type="cellIs" dxfId="1" priority="64" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="65" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E59">
+    <cfRule type="cellIs" dxfId="4" priority="61" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="62" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="63" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D60">
+    <cfRule type="cellIs" dxfId="0" priority="25" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="24" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60">
+    <cfRule type="cellIs" dxfId="2" priority="23" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="22" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="21" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D61">
+    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61">
+    <cfRule type="cellIs" dxfId="2" priority="18" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="17" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="16" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D62">
+    <cfRule type="cellIs" dxfId="1" priority="69" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="70" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E62">
+    <cfRule type="cellIs" dxfId="4" priority="66" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="67" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="68" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D63">
+    <cfRule type="cellIs" dxfId="1" priority="113" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="115" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E63">
+    <cfRule type="cellIs" dxfId="4" priority="107" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="109" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="111" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D64">
+    <cfRule type="cellIs" dxfId="1" priority="112" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="114" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E64">
+    <cfRule type="cellIs" dxfId="4" priority="106" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="108" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="110" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D65">
+    <cfRule type="cellIs" dxfId="1" priority="104" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="105" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E65">
+    <cfRule type="cellIs" dxfId="4" priority="101" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="102" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="103" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D66">
+    <cfRule type="cellIs" dxfId="1" priority="94" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="95" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E66">
+    <cfRule type="cellIs" dxfId="4" priority="91" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="92" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="93" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D67">
+    <cfRule type="cellIs" dxfId="1" priority="99" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="100" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E67">
+    <cfRule type="cellIs" dxfId="4" priority="96" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="97" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="98" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D68">
+    <cfRule type="cellIs" dxfId="1" priority="89" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="90" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E68">
+    <cfRule type="cellIs" dxfId="4" priority="86" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="87" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="88" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D69">
+    <cfRule type="cellIs" dxfId="1" priority="84" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="85" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E69">
+    <cfRule type="cellIs" dxfId="4" priority="81" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="82" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="83" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D70">
+    <cfRule type="cellIs" dxfId="1" priority="79" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="80" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E70">
+    <cfRule type="cellIs" dxfId="4" priority="76" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="77" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="78" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D71">
+    <cfRule type="cellIs" dxfId="1" priority="42" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="45" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E71">
+    <cfRule type="cellIs" dxfId="4" priority="33" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="36" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="39" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D72">
+    <cfRule type="cellIs" dxfId="1" priority="41" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="44" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E72">
+    <cfRule type="cellIs" dxfId="4" priority="32" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="35" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="38" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D73">
+    <cfRule type="cellIs" dxfId="1" priority="40" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="43" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E73">
+    <cfRule type="cellIs" dxfId="4" priority="31" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="34" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="37" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D74">
+    <cfRule type="cellIs" dxfId="1" priority="29" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="30" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E74">
+    <cfRule type="cellIs" dxfId="4" priority="26" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="27" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="28" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D75">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E75">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D49:D50">
+    <cfRule type="cellIs" dxfId="0" priority="158" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="157" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D56:D57">
+    <cfRule type="cellIs" dxfId="1" priority="124" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="125" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E49:E50">
+    <cfRule type="cellIs" dxfId="2" priority="156" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="155" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="154" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E56:E57">
+    <cfRule type="cellIs" dxfId="4" priority="121" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="122" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="123" operator="equal">
+      <formula>"整数"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D47 D76:D1048576">
+    <cfRule type="cellIs" dxfId="1" priority="229" operator="equal">
+      <formula>"Map"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="230" operator="equal">
+      <formula>"列表"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E47 E76:E1048576">
+    <cfRule type="cellIs" dxfId="4" priority="231" operator="equal">
+      <formula>"字符串"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="232" operator="equal">
+      <formula>"浮点数"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="233" operator="equal">
+      <formula>"整数"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -2300,6 +3482,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>